--- a/human_resources_forms/010_tech_startup_data_analyst_interview_form--human_resources_forms.xlsx
+++ b/human_resources_forms/010_tech_startup_data_analyst_interview_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>data_architectural</t>
+          <t>business_analyst</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Data Architectural</t>
+          <t>Business Analyst</t>
         </is>
       </c>
     </row>
@@ -1335,80 +1335,80 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>business_analyst</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>job_category_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>business_analyst</t>
+          <t>finance_and_banking</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Finance and Banking</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>job_category_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>business_analyst</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Retail</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>job_category_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>business_analyst</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Tech</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>job_category_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>finance_and_banking</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finance and Banking</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1437,78 +1437,10 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>job_category_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>tech</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Tech</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>job_category_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>marketing</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>job_category_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>job_category_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
